--- a/files/move_source.xlsx
+++ b/files/move_source.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9716EB87-278D-4D79-90E4-41DAC80A9B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9461F65D-0AE5-46DD-A167-8A5B539C4F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{61A5D644-8311-4CC4-B26A-0A9FF0AF014A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{265F2F45-1970-4BF5-A973-6E021EA40880}"/>
   </bookViews>
   <sheets>
     <sheet name="損益表" sheetId="1" r:id="rId1"/>
@@ -156,13 +156,13 @@
     <t>-已結案</t>
   </si>
   <si>
-    <t>這是來源檔的說明，會配對到目標的「說明」；測試時取消勾選，不要搬</t>
+    <t>這是來源檔的說明，會配對到目標的「說明」；測試時取消勾選，不要匯入</t>
   </si>
   <si>
     <t>這張表在目標沒有同名的工作表，應該被跳過</t>
   </si>
   <si>
-    <t>新資料 (目標有保護，不應該搬過去)</t>
+    <t>新資料 (目標有保護，不應該匯入)</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D4DC8-E705-4AE8-810B-653B5DD62F0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C77F39F-1918-43BE-9755-D96EC2163E3C}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -650,7 +650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7313465-1C7C-49BA-9250-127B4B271905}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54262F6A-70A2-476F-92FC-8256911374D1}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -734,7 +734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4406D596-6A8C-4ED4-A462-37DB4B511083}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABC2FA05-FBEE-4A6C-9774-FABE25E2599F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -750,7 +750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9603C528-41E2-40FA-BA3B-40EEC38F98CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA4772D-72B0-4F4A-B0A0-1EA0020BAB66}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -766,7 +766,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5363AE2-D435-41C4-BD3D-D8A105F40B83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D532BC1D-859D-48CD-8EA7-C4CCE6362F0A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -776,7 +776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8B07E7-F762-4ADB-8788-70571F6447D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBDE968A-4F27-4364-824E-91779D5BCE68}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
